--- a/test_cases/repeating_sections_per_tab/input.xlsx
+++ b/test_cases/repeating_sections_per_tab/input.xlsx
@@ -423,7 +423,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="D3" t="inlineStr">
         <is>
@@ -692,7 +691,6 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -773,7 +771,6 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -826,8 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="D22" t="inlineStr">
         <is>
@@ -835,7 +830,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="D24" t="inlineStr">
         <is>
@@ -886,7 +880,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DOCK #</t>
+          <t>DOCK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1042,7 +1036,6 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
